--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationratio-doseperday.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationratio-doseperday.xlsx
@@ -408,7 +408,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>量を理解し、表現する方法。 / How the Quantity should be understood and represented.</t>
+    <t>数量の評価解釈コード / How the Quantity should be understood and represented.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/quantity-comparator|4.0.1</t>
@@ -534,7 +534,7 @@
     <t>Ratio.denominator.comparator</t>
   </si>
   <si>
-    <t>&lt;|&lt;= |&gt; = |&gt;  - 価値を理解する方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
+    <t>&lt;|&lt;= |&gt; = |&gt;  - 値の比較方法 / &lt; | &lt;= | &gt;= | &gt; - how to understand the value</t>
   </si>
   <si>
     <t>値をどのように理解し、表現する必要があるか - 測定の問題により実際の値が記載されている値よりも大きいか小さいかどうか。例えばコンパレータが「&lt;」の場合、実際の値は&lt;stated値です。 / How the value should be understood and represented - whether the actual value is greater or less than the stated value due to measurement issues; e.g. if the comparator is "&lt;" , then the real value is &lt; stated value.</t>
@@ -895,43 +895,43 @@
   <dimension ref="A1:AL20"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="29.3828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="29.3828125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="25.1875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="25.1875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="72.0078125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="61.734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="226.484375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="194.171875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="70.171875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.89453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="20.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="57.328125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.63671875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="17.33984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="28.1484375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="68.94921875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="24.1328125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="59.11328125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationratio-doseperday.xlsx
+++ b/jpcore-r4/feature/swg45-FamilyMember-CS-Suppl/StructureDefinition-jp-medicationratio-doseperday.xlsx
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
